--- a/output/pdf_financials_xlsx/YNV.xlsx
+++ b/output/pdf_financials_xlsx/YNV.xlsx
@@ -6123,7 +6123,7 @@
         <v>-0.159751</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>0.07670299999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6145,46 +6145,46 @@
         <v>0.735151</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.762213</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.088</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.668405</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.597619</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.886382</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.084335</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.682102</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.570599</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>1.739389</v>
       </c>
     </row>
     <row r="93">
@@ -7678,13 +7678,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.1196</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.272498</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.026934</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -10768,7 +10768,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11044,7 +11048,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -16664,7 +16672,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17484,7 +17496,11 @@
           <t>Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18010,7 +18026,11 @@
           <t>Reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -19172,7 +19192,11 @@
           <t>Reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -19492,7 +19516,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -21386,7 +21414,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -22126,7 +22158,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -22858,7 +22894,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23790,7 +23830,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -38536,7 +38580,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -39492,7 +39540,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YNV.xlsx
+++ b/output/pdf_financials_xlsx/YNV.xlsx
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.469738</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.161974</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.034093</v>
@@ -2544,22 +2544,22 @@
         <v>0.008045</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.019969</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.014755</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.004521</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003453</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.957078</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>2.126725</v>
@@ -2580,7 +2580,7 @@
         <v>3.348851</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.327538</v>
       </c>
     </row>
     <row r="35">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.469738</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.161974</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.034093</v>
@@ -2666,22 +2666,22 @@
         <v>0.008045</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.019969</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.014755</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.004521</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003453</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.957078</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>2.126725</v>
@@ -2702,7 +2702,7 @@
         <v>3.348851</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.327538</v>
       </c>
     </row>
     <row r="37">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.485732</v>
+        <v>0.015994</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.191578</v>
+        <v>0.029604</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.08448600000000001</v>
@@ -3398,13 +3398,13 @@
         <v>0.020988</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.015964</v>
+        <v>0.014967</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.030692</v>
+        <v>0.010723</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.019997</v>
+        <v>0.005242</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.967777</v>
+        <v>0.010699</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.174304</v>
@@ -3434,7 +3434,7 @@
         <v>0.106781</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.570995</v>
+        <v>0.243457</v>
       </c>
     </row>
     <row r="49">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24244,7 +24244,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">

--- a/output/pdf_financials_xlsx/YNV.xlsx
+++ b/output/pdf_financials_xlsx/YNV.xlsx
@@ -6632,31 +6632,31 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.023673</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003699</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01262</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.004417</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.005927</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.005754</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006777</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.005481</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.004352</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0.011564</v>
@@ -6949,19 +6949,19 @@
         <v>-0.5028280000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.093225</v>
+        <v>-0.087298</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.116698</v>
+        <v>0.122452</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.063375</v>
+        <v>0.056598</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.13999</v>
+        <v>0.145471</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.138728</v>
+        <v>-0.134376</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.210731</v>
@@ -7580,25 +7580,25 @@
         <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.009920999999999999</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.151914</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.115902</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.005049</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.006586</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001419</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>0</v>
+        <v>-0.003947</v>
       </c>
     </row>
     <row r="117">
@@ -18778,7 +18778,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -27468,7 +27472,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -29158,7 +29166,11 @@
           <t>Finders’ warrants issued for private placement $</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -32490,7 +32502,11 @@
           <t>Finders’ shares issued for private placement $</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32594,7 +32610,11 @@
           <t>Value of finders’ warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -34388,7 +34408,11 @@
           <t>Value of warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34494,7 +34518,11 @@
           <t>Finders’ unit issued for private placement $</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -35640,7 +35668,11 @@
           <t>Shares issued for finder's fees for private placement $</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -35746,7 +35778,11 @@
           <t>Value of finder’s warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36696,7 +36732,11 @@
           <t>Shares issued for finder's fees for private placement (Note 11) $</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -37014,7 +37054,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -39330,7 +39374,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -40496,7 +40544,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -44290,7 +44342,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E343" s="5" t="n">
         <v>0.023673</v>
       </c>
@@ -46536,7 +46592,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
